--- a/GF_X-master/AAAGameData/Languages/Japanese.xlsx
+++ b/GF_X-master/AAAGameData/Languages/Japanese.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>BRAKE</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>エンジン台</t>
+  </si>
+  <si>
+    <t>FailGame</t>
+  </si>
+  <si>
+    <t>あなたはボスに発見されて、すぐに除名されて、それから街頭に流れて、再び時間を逆転することをクリックします</t>
   </si>
   <si>
     <t>GET</t>
@@ -119,6 +125,12 @@
     <t>クリックして開始</t>
   </si>
   <si>
+    <t>Nice</t>
+  </si>
+  <si>
+    <t>よくやった！</t>
+  </si>
+  <si>
     <t>Nothing</t>
   </si>
   <si>
@@ -141,12 +153,6 @@
   </si>
   <si>
     <t>キャンセル</t>
-  </si>
-  <si>
-    <t>RatingDialog.Description</t>
-  </si>
-  <si>
-    <t>このゲームは好きですか。\n 5つ星を評価してください！</t>
   </si>
   <si>
     <t>RatingDialog.HighRatingTips</t>
@@ -239,6 +245,12 @@
     <t>ドライブ</t>
   </si>
   <si>
+    <t>SuccessGame</t>
+  </si>
+  <si>
+    <t>あなたはボスの娘の心を虜にすることに成功し、すぐに白富美と結婚し、それから人生の頂点に向かった</t>
+  </si>
+  <si>
     <t>TermsOfService</t>
   </si>
   <si>
@@ -248,13 +260,13 @@
     <t>Test123</t>
   </si>
   <si>
-    <t>言語スキャンのテスト</t>
+    <t>コードテスト言語スキャン</t>
   </si>
   <si>
-    <t>Test1234</t>
+    <t>TipStart</t>
   </si>
   <si>
-    <t/>
+    <t>明ちゃんをクリックしてキスして、でもボスに気をつけて！またドアや窓にも注意！</t>
   </si>
   <si>
     <t>UNLOCK</t>
@@ -424,6 +436,14 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -1691,6 +1711,1002 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -1707,265 +2723,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1058">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1058"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1059">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1059"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1060">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1060"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1061">
+            <xdr:cNvPr hidden="1" name="A1" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1061"/>
@@ -2040,18 +2798,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1062">
+            <xdr:cNvPr hidden="1" name="A2" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1062"/>
@@ -2126,18 +2884,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1063">
+            <xdr:cNvPr hidden="1" name="A3" id="1063">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1063"/>
@@ -2212,18 +2970,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1064">
+            <xdr:cNvPr hidden="1" name="A4" id="1064">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1064"/>
@@ -2298,18 +3056,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1065">
+            <xdr:cNvPr hidden="1" name="A5" id="1065">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1065"/>
@@ -2384,18 +3142,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1066">
+            <xdr:cNvPr hidden="1" name="A6" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1066"/>
@@ -2470,18 +3228,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1067">
+            <xdr:cNvPr hidden="1" name="A7" id="1067">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1067"/>
@@ -2556,18 +3314,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1068">
+            <xdr:cNvPr hidden="1" name="A8" id="1068">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1068"/>
@@ -2642,18 +3400,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1069">
+            <xdr:cNvPr hidden="1" name="A9" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1069"/>
@@ -2728,18 +3486,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1070">
+            <xdr:cNvPr hidden="1" name="A10" id="1070">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1070"/>
@@ -2814,18 +3572,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1071">
+            <xdr:cNvPr hidden="1" name="A11" id="1071">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1071"/>
@@ -2900,18 +3658,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1072">
+            <xdr:cNvPr hidden="1" name="A12" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1072"/>
@@ -2986,18 +3744,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1073">
+            <xdr:cNvPr hidden="1" name="A13" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1073"/>
@@ -3072,18 +3830,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1074">
+            <xdr:cNvPr hidden="1" name="A14" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1074"/>
@@ -3158,18 +3916,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1075">
+            <xdr:cNvPr hidden="1" name="A15" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1075"/>
@@ -3244,18 +4002,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1076">
+            <xdr:cNvPr hidden="1" name="A16" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1076"/>
@@ -3330,18 +4088,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1077">
+            <xdr:cNvPr hidden="1" name="A17" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1077"/>
@@ -3416,18 +4174,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1078">
+            <xdr:cNvPr hidden="1" name="A18" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1078"/>
@@ -3502,18 +4260,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1079">
+            <xdr:cNvPr hidden="1" name="A19" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1079"/>
@@ -3588,18 +4346,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1080">
+            <xdr:cNvPr hidden="1" name="A20" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1080"/>
@@ -3674,18 +4432,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1081">
+            <xdr:cNvPr hidden="1" name="A21" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1081"/>
@@ -3760,18 +4518,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1082">
+            <xdr:cNvPr hidden="1" name="A22" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1082"/>
@@ -3846,18 +4604,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1083">
+            <xdr:cNvPr hidden="1" name="A23" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1083"/>
@@ -3932,18 +4690,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1084">
+            <xdr:cNvPr hidden="1" name="A24" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1084"/>
@@ -4018,18 +4776,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1085">
+            <xdr:cNvPr hidden="1" name="A25" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1085"/>
@@ -4104,18 +4862,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1086">
+            <xdr:cNvPr hidden="1" name="A26" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1086"/>
@@ -4190,18 +4948,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1087">
+            <xdr:cNvPr hidden="1" name="A27" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1087"/>
@@ -4276,18 +5034,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1088">
+            <xdr:cNvPr hidden="1" name="A28" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1088"/>
@@ -4362,18 +5120,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1089">
+            <xdr:cNvPr hidden="1" name="A29" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1089"/>
@@ -4448,6 +5206,264 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>30</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A30" id="1090">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1090"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>30</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>31</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A31" id="1091">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1091"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>31</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>32</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A32" id="1092">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1092"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -4459,10 +5475,182 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1090">
+            <xdr:cNvPr hidden="1" name="A33" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1090"/>
+                  <a14:compatExt spid="_x0000_s1093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A34" id="1094">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1094"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>35</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A35" id="1095">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1095"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4794,7 +5982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -5099,6 +6287,24 @@
         <v>65</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="1"/>
+      <c r="B34" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1"/>
+      <c r="B35" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5111,7 +6317,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId305" name="A1">
+            <control shapeId="1061" r:id="rId547" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5133,7 +6339,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId306" name="A2">
+            <control shapeId="1062" r:id="rId548" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5155,7 +6361,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId307" name="A3">
+            <control shapeId="1063" r:id="rId549" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5177,7 +6383,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId308" name="A4">
+            <control shapeId="1064" r:id="rId550" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5199,7 +6405,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId309" name="A5">
+            <control shapeId="1065" r:id="rId551" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5221,7 +6427,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId310" name="A6">
+            <control shapeId="1066" r:id="rId552" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5243,7 +6449,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId311" name="A7">
+            <control shapeId="1067" r:id="rId553" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5265,7 +6471,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId312" name="A8">
+            <control shapeId="1068" r:id="rId554" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5287,7 +6493,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId313" name="A9">
+            <control shapeId="1069" r:id="rId555" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5309,7 +6515,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId314" name="A10">
+            <control shapeId="1070" r:id="rId556" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5331,7 +6537,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId315" name="A11">
+            <control shapeId="1071" r:id="rId557" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5353,7 +6559,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId316" name="A12">
+            <control shapeId="1072" r:id="rId558" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5375,7 +6581,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId317" name="A13">
+            <control shapeId="1073" r:id="rId559" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5397,7 +6603,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId318" name="A14">
+            <control shapeId="1074" r:id="rId560" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5419,7 +6625,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId319" name="A15">
+            <control shapeId="1075" r:id="rId561" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5441,7 +6647,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId320" name="A16">
+            <control shapeId="1076" r:id="rId562" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5463,7 +6669,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId321" name="A17">
+            <control shapeId="1077" r:id="rId563" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5485,7 +6691,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId322" name="A18">
+            <control shapeId="1078" r:id="rId564" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5507,7 +6713,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId323" name="A19">
+            <control shapeId="1079" r:id="rId565" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5529,7 +6735,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId324" name="A20">
+            <control shapeId="1080" r:id="rId566" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5551,7 +6757,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId325" name="A21">
+            <control shapeId="1081" r:id="rId567" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5573,7 +6779,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId326" name="A22">
+            <control shapeId="1082" r:id="rId568" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5595,7 +6801,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId327" name="A23">
+            <control shapeId="1083" r:id="rId569" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5617,7 +6823,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId328" name="A24">
+            <control shapeId="1084" r:id="rId570" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5639,7 +6845,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId329" name="A25">
+            <control shapeId="1085" r:id="rId571" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5661,7 +6867,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId330" name="A26">
+            <control shapeId="1086" r:id="rId572" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5683,7 +6889,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId331" name="A27">
+            <control shapeId="1087" r:id="rId573" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5705,7 +6911,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId332" name="A28">
+            <control shapeId="1088" r:id="rId574" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5727,7 +6933,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId333" name="A29">
+            <control shapeId="1089" r:id="rId575" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5749,7 +6955,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId334" name="A30">
+            <control shapeId="1090" r:id="rId576" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5771,7 +6977,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId335" name="A31">
+            <control shapeId="1091" r:id="rId577" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5793,7 +6999,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId336" name="A32">
+            <control shapeId="1092" r:id="rId578" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5815,7 +7021,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId337" name="A33">
+            <control shapeId="1093" r:id="rId579" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5835,6 +7041,50 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1094" r:id="rId580" name="A34">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>33</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>34</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1095" r:id="rId581" name="A35">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>34</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>35</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>

--- a/GF_X-master/AAAGameData/Languages/Japanese.xlsx
+++ b/GF_X-master/AAAGameData/Languages/Japanese.xlsx
@@ -2707,6 +2707,286 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -2723,7 +3003,93 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1061">
+            <xdr:cNvPr hidden="1" name="A1" id="1060">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1060"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A2" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1061"/>
@@ -2798,18 +3164,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1062">
+            <xdr:cNvPr hidden="1" name="A3" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1062"/>
@@ -2884,18 +3250,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1063">
+            <xdr:cNvPr hidden="1" name="A4" id="1063">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1063"/>
@@ -2970,18 +3336,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1064">
+            <xdr:cNvPr hidden="1" name="A5" id="1064">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1064"/>
@@ -3056,18 +3422,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1065">
+            <xdr:cNvPr hidden="1" name="A6" id="1065">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1065"/>
@@ -3142,18 +3508,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1066">
+            <xdr:cNvPr hidden="1" name="A7" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1066"/>
@@ -3228,18 +3594,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1067">
+            <xdr:cNvPr hidden="1" name="A8" id="1067">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1067"/>
@@ -3314,18 +3680,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1068">
+            <xdr:cNvPr hidden="1" name="A9" id="1068">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1068"/>
@@ -3400,18 +3766,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1069">
+            <xdr:cNvPr hidden="1" name="A10" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1069"/>
@@ -3486,18 +3852,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1070">
+            <xdr:cNvPr hidden="1" name="A11" id="1070">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1070"/>
@@ -3572,18 +3938,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1071">
+            <xdr:cNvPr hidden="1" name="A12" id="1071">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1071"/>
@@ -3658,18 +4024,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1072">
+            <xdr:cNvPr hidden="1" name="A13" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1072"/>
@@ -3744,18 +4110,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1073">
+            <xdr:cNvPr hidden="1" name="A14" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1073"/>
@@ -3830,18 +4196,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1074">
+            <xdr:cNvPr hidden="1" name="A15" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1074"/>
@@ -3916,18 +4282,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1075">
+            <xdr:cNvPr hidden="1" name="A16" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1075"/>
@@ -4002,18 +4368,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1076">
+            <xdr:cNvPr hidden="1" name="A17" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1076"/>
@@ -4088,18 +4454,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1077">
+            <xdr:cNvPr hidden="1" name="A18" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1077"/>
@@ -4174,18 +4540,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1078">
+            <xdr:cNvPr hidden="1" name="A19" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1078"/>
@@ -4260,18 +4626,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1079">
+            <xdr:cNvPr hidden="1" name="A20" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1079"/>
@@ -4346,18 +4712,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1080">
+            <xdr:cNvPr hidden="1" name="A21" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1080"/>
@@ -4432,18 +4798,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1081">
+            <xdr:cNvPr hidden="1" name="A22" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1081"/>
@@ -4518,18 +4884,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1082">
+            <xdr:cNvPr hidden="1" name="A23" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1082"/>
@@ -4604,18 +4970,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1083">
+            <xdr:cNvPr hidden="1" name="A24" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1083"/>
@@ -4690,18 +5056,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1084">
+            <xdr:cNvPr hidden="1" name="A25" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1084"/>
@@ -4776,18 +5142,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1085">
+            <xdr:cNvPr hidden="1" name="A26" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1085"/>
@@ -4862,18 +5228,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1086">
+            <xdr:cNvPr hidden="1" name="A27" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1086"/>
@@ -4948,18 +5314,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1087">
+            <xdr:cNvPr hidden="1" name="A28" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1087"/>
@@ -5034,18 +5400,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1088">
+            <xdr:cNvPr hidden="1" name="A29" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1088"/>
@@ -5120,18 +5486,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1089">
+            <xdr:cNvPr hidden="1" name="A30" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1089"/>
@@ -5206,18 +5572,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1090">
+            <xdr:cNvPr hidden="1" name="A31" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1090"/>
@@ -5292,18 +5658,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1091">
+            <xdr:cNvPr hidden="1" name="A32" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1091"/>
@@ -5378,18 +5744,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1092">
+            <xdr:cNvPr hidden="1" name="A33" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -5464,18 +5830,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1093">
+            <xdr:cNvPr hidden="1" name="A34" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -5550,92 +5916,6 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1094">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1094"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
           <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -5647,10 +5927,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1095">
+            <xdr:cNvPr hidden="1" name="A35" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1095"/>
+                  <a14:compatExt spid="_x0000_s1094"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6317,7 +6597,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId547" name="A1">
+            <control shapeId="1060" r:id="rId615" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6339,7 +6619,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId548" name="A2">
+            <control shapeId="1061" r:id="rId616" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6361,7 +6641,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId549" name="A3">
+            <control shapeId="1062" r:id="rId617" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6383,7 +6663,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId550" name="A4">
+            <control shapeId="1063" r:id="rId618" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6405,7 +6685,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId551" name="A5">
+            <control shapeId="1064" r:id="rId619" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6427,7 +6707,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId552" name="A6">
+            <control shapeId="1065" r:id="rId620" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6449,7 +6729,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId553" name="A7">
+            <control shapeId="1066" r:id="rId621" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6471,7 +6751,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId554" name="A8">
+            <control shapeId="1067" r:id="rId622" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6493,7 +6773,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId555" name="A9">
+            <control shapeId="1068" r:id="rId623" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6515,7 +6795,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId556" name="A10">
+            <control shapeId="1069" r:id="rId624" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6537,7 +6817,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId557" name="A11">
+            <control shapeId="1070" r:id="rId625" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6559,7 +6839,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId558" name="A12">
+            <control shapeId="1071" r:id="rId626" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6581,7 +6861,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId559" name="A13">
+            <control shapeId="1072" r:id="rId627" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6603,7 +6883,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId560" name="A14">
+            <control shapeId="1073" r:id="rId628" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6625,7 +6905,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId561" name="A15">
+            <control shapeId="1074" r:id="rId629" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6647,7 +6927,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId562" name="A16">
+            <control shapeId="1075" r:id="rId630" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6669,7 +6949,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId563" name="A17">
+            <control shapeId="1076" r:id="rId631" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6691,7 +6971,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId564" name="A18">
+            <control shapeId="1077" r:id="rId632" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6713,7 +6993,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId565" name="A19">
+            <control shapeId="1078" r:id="rId633" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6735,7 +7015,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId566" name="A20">
+            <control shapeId="1079" r:id="rId634" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6757,7 +7037,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId567" name="A21">
+            <control shapeId="1080" r:id="rId635" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6779,7 +7059,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId568" name="A22">
+            <control shapeId="1081" r:id="rId636" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6801,7 +7081,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId569" name="A23">
+            <control shapeId="1082" r:id="rId637" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6823,7 +7103,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId570" name="A24">
+            <control shapeId="1083" r:id="rId638" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6845,7 +7125,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId571" name="A25">
+            <control shapeId="1084" r:id="rId639" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6867,7 +7147,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId572" name="A26">
+            <control shapeId="1085" r:id="rId640" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6889,7 +7169,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId573" name="A27">
+            <control shapeId="1086" r:id="rId641" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6911,7 +7191,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId574" name="A28">
+            <control shapeId="1087" r:id="rId642" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6933,7 +7213,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId575" name="A29">
+            <control shapeId="1088" r:id="rId643" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6955,7 +7235,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId576" name="A30">
+            <control shapeId="1089" r:id="rId644" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6977,7 +7257,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId577" name="A31">
+            <control shapeId="1090" r:id="rId645" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6999,7 +7279,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId578" name="A32">
+            <control shapeId="1091" r:id="rId646" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7021,7 +7301,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId579" name="A33">
+            <control shapeId="1092" r:id="rId647" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7043,7 +7323,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId580" name="A34">
+            <control shapeId="1093" r:id="rId648" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7065,7 +7345,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId581" name="A35">
+            <control shapeId="1094" r:id="rId649" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
